--- a/reports/pdf_change_20260902.xlsx
+++ b/reports/pdf_change_20260902.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,489억   ·   현금 35억(0.8%)      당일 2026-09-02  vs  전영업일 2026-09-01      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,489억      당일 2026-09-02  vs  전영업일 2026-09-01      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -779,7 +779,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,768억   ·   현금 12억(0.3%)      당일 2026-09-02  vs  전영업일 2026-09-01      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,768억      당일 2026-09-02  vs  전영업일 2026-09-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -803,7 +803,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억   ·   현금 44억(1.8%)      당일 2026-09-02  vs  전영업일 2026-09-01      매수 2종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억      당일 2026-09-02  vs  전영업일 2026-09-01      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1036,7 +1036,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,141억   ·   현금 27억(1.3%)      당일 2026-09-02  vs  전영업일 2026-09-01      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,141억      당일 2026-09-02  vs  전영업일 2026-09-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1060,7 +1060,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 1억(0.5%)      당일 2026-09-02  vs  전영업일 2026-09-01      매수 4종목  /  매도 1종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억      당일 2026-09-02  vs  전영업일 2026-09-01      매수 4종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1277,7 +1277,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 535억   ·   현금 4억(0.7%)      당일 2026-09-02  vs  전영업일 2026-09-01      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 535억      당일 2026-09-02  vs  전영업일 2026-09-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
